--- a/sources/bryan_step3.xlsx
+++ b/sources/bryan_step3.xlsx
@@ -685,6 +685,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>74993c60-9c25-4ff3-b3fa-f1296b65505c</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>74993c60-9c25-4ff3-b3fa-f1296b65505c</t>
@@ -722,6 +727,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>09ebf217-6f8c-49a1-9120-b6d903c7cee0</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>09ebf217-6f8c-49a1-9120-b6d903c7cee0</t>
@@ -757,6 +767,11 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>e28da776-8eb0-403d-bcb0-31b6cdece7b8</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -5500,6 +5515,11 @@
           <t>hmmmhhhhmh</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>1e24fe73-69af-4506-9a4b-0118515b9e02</t>
+        </is>
+      </c>
       <c r="O108" t="inlineStr">
         <is>
           <t>1e24fe73-69af-4506-9a4b-0118515b9e02</t>
@@ -5527,6 +5547,11 @@
           <t>hmmmhhhm</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>ef6f4e30-fc93-476d-aa40-bed23e6e262d</t>
+        </is>
+      </c>
       <c r="O109" t="inlineStr">
         <is>
           <t>ef6f4e30-fc93-476d-aa40-bed23e6e262d</t>
@@ -5552,6 +5577,11 @@
       <c r="I110" t="inlineStr">
         <is>
           <t>hmmmhhmh</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>f4a77540-d285-4628-a209-f8f0a4fbebf3</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
